--- a/MMU Config Options.xlsx
+++ b/MMU Config Options.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_PDh\_cwg-base__Home\Computer Archtecture\Retro Computing\SBC6502\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\_cwg-base__Home\Computer Archtecture\Retro Computing\SBC6502\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73FD1858-8F58-48C7-BE43-EA18C4E7675E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10BFE499-461A-4C1A-B3DE-6A84A13FF8E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2014" yWindow="1046" windowWidth="19097" windowHeight="11785" xr2:uid="{E2CDCCBC-594B-4A42-BA3F-95D5E3C9B4E3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E2CDCCBC-594B-4A42-BA3F-95D5E3C9B4E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -89,12 +89,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -109,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -123,9 +129,20 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -440,131 +457,132 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28045FA7-E967-4EB5-BE87-47BB5AA2AF07}">
-  <dimension ref="A1:O5"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:O6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.3046875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.69140625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="12.69140625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="8.69140625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="12.69140625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="8.69140625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="12.69140625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="8.69140625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="12.69140625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="8.69140625" customWidth="1"/>
-    <col min="11" max="11" width="12.69140625" customWidth="1"/>
-    <col min="12" max="12" width="8.69140625" customWidth="1"/>
-    <col min="13" max="13" width="12.69140625" customWidth="1"/>
+    <col min="1" max="1" width="21.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.6640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="6" customWidth="1"/>
+    <col min="4" max="4" width="8.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="12.6640625" style="6" customWidth="1"/>
+    <col min="6" max="6" width="8.6640625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" style="6" customWidth="1"/>
+    <col min="8" max="8" width="8.6640625" style="6" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" style="6" customWidth="1"/>
+    <col min="10" max="10" width="8.6640625" customWidth="1"/>
+    <col min="11" max="11" width="12.6640625" style="7" customWidth="1"/>
+    <col min="12" max="12" width="8.6640625" style="7" customWidth="1"/>
+    <col min="13" max="13" width="12.6640625" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="B1" s="5" t="s">
+    <row r="1" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="8"/>
+      <c r="B1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5" t="s">
+      <c r="C1" s="9"/>
+      <c r="D1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5" t="s">
+      <c r="E1" s="9"/>
+      <c r="F1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5" t="s">
+      <c r="G1" s="9"/>
+      <c r="H1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5" t="s">
+      <c r="I1" s="9"/>
+      <c r="J1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5" t="s">
+      <c r="K1" s="9"/>
+      <c r="L1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="M1" s="5"/>
+      <c r="M1" s="9"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>0</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>0</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="5" t="s">
         <v>0</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
       <c r="B3" s="2">
         <v>16</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="6">
         <f t="shared" ref="C3:C5" si="0">2^B3</f>
         <v>65536</v>
       </c>
       <c r="D3" s="2">
         <v>20</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="6">
         <f t="shared" ref="E3" si="1">2^D3</f>
         <v>1048576</v>
       </c>
       <c r="F3" s="2">
         <v>10</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="6">
         <f t="shared" ref="G3" si="2">2^F3</f>
         <v>1024</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="6">
         <f>D3-F3</f>
         <v>10</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3" s="6">
         <f t="shared" ref="I3" si="3">2^H3</f>
         <v>1024</v>
       </c>
       <c r="J3" s="2">
         <v>6</v>
       </c>
-      <c r="K3" s="2">
+      <c r="K3" s="6">
         <f t="shared" ref="K3" si="4">2^J3</f>
         <v>64</v>
       </c>
-      <c r="L3" s="2">
+      <c r="L3" s="6">
         <f>B3-F3+J3</f>
         <v>12</v>
       </c>
-      <c r="M3" s="2">
+      <c r="M3" s="6">
         <f>2^L3</f>
         <v>4096</v>
       </c>
@@ -573,49 +591,49 @@
         <v>8192</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
       <c r="B4" s="2">
         <v>16</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="6">
         <f t="shared" si="0"/>
         <v>65536</v>
       </c>
       <c r="D4" s="2">
         <v>20</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="6">
         <f t="shared" ref="E4" si="5">2^D4</f>
         <v>1048576</v>
       </c>
       <c r="F4" s="2">
         <v>10</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="6">
         <f t="shared" ref="G4" si="6">2^F4</f>
         <v>1024</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="6">
         <f>D4-F4</f>
         <v>10</v>
       </c>
-      <c r="I4" s="2">
+      <c r="I4" s="6">
         <f t="shared" ref="I4" si="7">2^H4</f>
         <v>1024</v>
       </c>
       <c r="J4" s="2">
         <v>1</v>
       </c>
-      <c r="K4" s="2">
+      <c r="K4" s="6">
         <f t="shared" ref="K4" si="8">2^J4</f>
         <v>2</v>
       </c>
-      <c r="L4" s="2">
+      <c r="L4" s="6">
         <f>B4-F4+J4</f>
         <v>7</v>
       </c>
-      <c r="M4" s="2">
+      <c r="M4" s="6">
         <f t="shared" ref="M4" si="9">2^L4</f>
         <v>128</v>
       </c>
@@ -624,54 +642,105 @@
         <v>256</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" s="2">
         <v>16</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="6">
         <f t="shared" si="0"/>
         <v>65536</v>
       </c>
       <c r="D5" s="2">
         <v>20</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="6">
         <f t="shared" ref="E5" si="11">2^D5</f>
         <v>1048576</v>
       </c>
       <c r="F5" s="2">
         <v>9</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="6">
         <f t="shared" ref="G5" si="12">2^F5</f>
         <v>512</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="6">
         <f>D5-F5</f>
         <v>11</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I5" s="6">
         <f t="shared" ref="I5" si="13">2^H5</f>
         <v>2048</v>
       </c>
       <c r="J5" s="2">
         <v>6</v>
       </c>
-      <c r="K5" s="2">
+      <c r="K5" s="6">
         <f t="shared" ref="K5" si="14">2^J5</f>
         <v>64</v>
       </c>
-      <c r="L5" s="2">
+      <c r="L5" s="6">
         <f>B5-F5+J5</f>
         <v>13</v>
       </c>
-      <c r="M5" s="2">
+      <c r="M5" s="6">
         <f t="shared" ref="M5" si="15">2^L5</f>
         <v>8192</v>
       </c>
       <c r="O5">
         <f t="shared" si="10"/>
+        <v>16384</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A6" s="3"/>
+      <c r="B6" s="2">
+        <v>16</v>
+      </c>
+      <c r="C6" s="6">
+        <f t="shared" ref="C6" si="16">2^B6</f>
+        <v>65536</v>
+      </c>
+      <c r="D6" s="2">
+        <v>24</v>
+      </c>
+      <c r="E6" s="6">
+        <f t="shared" ref="E6" si="17">2^D6</f>
+        <v>16777216</v>
+      </c>
+      <c r="F6" s="2">
+        <v>9</v>
+      </c>
+      <c r="G6" s="6">
+        <f t="shared" ref="G6" si="18">2^F6</f>
+        <v>512</v>
+      </c>
+      <c r="H6" s="6">
+        <f>D6-F6</f>
+        <v>15</v>
+      </c>
+      <c r="I6" s="6">
+        <f t="shared" ref="I6" si="19">2^H6</f>
+        <v>32768</v>
+      </c>
+      <c r="J6" s="2">
+        <v>6</v>
+      </c>
+      <c r="K6" s="6">
+        <f t="shared" ref="K6" si="20">2^J6</f>
+        <v>64</v>
+      </c>
+      <c r="L6" s="6">
+        <f>B6-F6+J6</f>
+        <v>13</v>
+      </c>
+      <c r="M6" s="6">
+        <f t="shared" ref="M6" si="21">2^L6</f>
+        <v>8192</v>
+      </c>
+      <c r="O6">
+        <f t="shared" ref="O6" si="22">2*M6</f>
         <v>16384</v>
       </c>
     </row>
